--- a/data/tags/אלבומים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BTS Arirang</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/bts-arirang/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום Arirang של BTS (שיצא במרץ 2026) הפך בתוך שבועות ספורים לאחד התקליטים המבוקשים בעולם גם פיזית (ויניל/מהדורות אספנים) וגם סטרימינג, וזה לא במקרה. מדובר בשילוב נדיר של אירוע תרבותי, מהלך מוזיקלי מחושב, ורגע רגשי של קאמבק. בעיני המעריצים, זה</v>
+        <v>21:10</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>BTS Arirang</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23054&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>08:36</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-04-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:10</v>
+        <v>21:11</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>ריי – This Music May Contain Hope</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%99%d7%99-this-music-may-contain-hope/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:11</v>
+        <v>האלבום "This Music May Contain Hope" של  ריי RAYE הוא יצירה טעונה רגשית, שממשיכה את הקו האישי והחשוף שהיא ביססה מאז הפריצה העצמאית שלה. כבר בשם יש פרובוקציה עדינה: במקום אזהרה שלילית (“עלול להכיל תכנים קשים”), היא מציעה אפשרות הפוכה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>ריי – This Music May Contain Hope</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=21671&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>11:50</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>